--- a/RoadmapSSI.xlsx
+++ b/RoadmapSSI.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
   <si>
     <t xml:space="preserve">Sprint</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t xml:space="preserve">Documento de viabilidad y pinout asignado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
   </si>
   <si>
     <t xml:space="preserve">S2</t>
@@ -296,7 +299,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -319,7 +321,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -327,7 +328,6 @@
       <color rgb="FF000000"/>
       <name val="Cambria"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -335,21 +335,18 @@
       <color rgb="FF000000"/>
       <name val="Cambria"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -357,7 +354,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -365,7 +361,6 @@
       <color rgb="FFC0392B"/>
       <name val="Cambria"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -530,140 +525,148 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -780,16 +783,16 @@
         <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -797,67 +800,25 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -876,35 +837,11 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -919,930 +856,933 @@
   <dimension ref="A1:R43"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="6" style="0" width="4.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="6" style="1" width="4.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4" t="n">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="Q2" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="5" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
+      <c r="F5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
+      <c r="E6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="A7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
+      <c r="E7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
+      <c r="E9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="14" t="s">
+      <c r="A10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
+      <c r="E10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
+      <c r="E11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="A12" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
+      <c r="E12" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
+      <c r="E13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="14" t="s">
+      <c r="A14" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
+      <c r="E14" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
+      <c r="E15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="A16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
+      <c r="E16" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
+      <c r="E18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="14" t="s">
+      <c r="A19" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
+      <c r="E19" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
+      <c r="E20" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="A21" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
+      <c r="E21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
+      <c r="E22" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="14" t="s">
+      <c r="A23" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
+      <c r="E23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
+      <c r="E24" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="14" t="s">
+      <c r="A25" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
+      <c r="E25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="22"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="24"/>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="11"/>
+      <c r="E27" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="A28" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
+      <c r="E28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="11"/>
+      <c r="E29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="s">
+      <c r="A31" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
+      <c r="B32" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="68.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="27" t="s">
+      <c r="A33" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="27"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="28" t="s">
+      <c r="B33" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="K33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="R33" s="3"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="R33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="29"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="K34" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="K34" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="M34" s="3"/>
-      <c r="R34" s="3"/>
+      <c r="M34" s="4"/>
+      <c r="R34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="82.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="27" t="s">
+      <c r="A35" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="27"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="M35" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="R35" s="3"/>
+      <c r="B35" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="29"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="M35" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="R35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="27" t="s">
+      <c r="A36" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="R36" s="28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="24" t="s">
+      <c r="B36" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-    </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="29" t="s">
+      <c r="C36" s="29"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="R36" s="30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="30" t="s">
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="30"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="30" t="s">
+      <c r="B39" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="30" t="s">
+      <c r="C39" s="32"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="30"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="30" t="s">
+      <c r="C40" s="32"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="30"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B43" s="30" t="s">
+      <c r="C41" s="32"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="30"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="32"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/RoadmapSSI.xlsx
+++ b/RoadmapSSI.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">S1</t>
   </si>
   <si>
-    <t xml:space="preserve">Cotizar componentes (IIS3DWB, INMP441, LDO), flex y conectores.</t>
+    <t xml:space="preserve">Cotizar componentes (INMP441, LDO, AFE sEMG) y conectores.</t>
   </si>
   <si>
     <t xml:space="preserve">BOM (Bill of Materials) final</t>
@@ -82,10 +82,10 @@
     <t xml:space="preserve">S3</t>
   </si>
   <si>
-    <t xml:space="preserve">Integración SPI DMA (Accel) e I2S DMA (Audio) con buffers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lectura sincronizada de IIS3DWB e INMP441</t>
+    <t xml:space="preserve">Integración ADC DMA (sEMG 4 canales) e I2S DMA (Audio) con buffers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lectura sincronizada de sEMG (4 canales) e INMP441</t>
   </si>
   <si>
     <t xml:space="preserve">Inicialización MIPI CSI y codec H.264 (128x128x1).</t>
@@ -127,7 +127,7 @@
     <t xml:space="preserve">S6</t>
   </si>
   <si>
-    <t xml:space="preserve">Ensamblaje final del prototipo en placa flex.</t>
+    <t xml:space="preserve">Ensamblaje final del prototipo (AFE sEMG en perfboard).</t>
   </si>
   <si>
     <t xml:space="preserve">Prototipo físico montado</t>
